--- a/docs/INVENTARIO-BANCO-DEMO.xlsx
+++ b/docs/INVENTARIO-BANCO-DEMO.xlsx
@@ -7,11 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario (demo)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen provisional" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Inventario demo" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inventario (demo)'!$A$5:$R$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Inventario demo'!$A$5:$V$77</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -19,10 +18,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0%"/>
-  </numFmts>
-  <fonts count="7">
+  <numFmts count="0"/>
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -33,11 +30,11 @@
     <font>
       <b val="1"/>
       <color rgb="00DC2626"/>
-      <sz val="13"/>
+      <sz val="12"/>
     </font>
     <font>
       <color rgb="006B7280"/>
-      <sz val="10"/>
+      <sz val="9"/>
     </font>
     <font>
       <b val="1"/>
@@ -45,16 +42,7 @@
       <sz val="10"/>
     </font>
     <font>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="00DC2626"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
+      <sz val="9"/>
     </font>
   </fonts>
   <fills count="3">
@@ -96,7 +84,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -104,10 +92,6 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -473,139 +457,163 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R65"/>
+  <dimension ref="A1:V77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
-    <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="24" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
     <col width="26" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="24" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-    <col width="13" customWidth="1" min="10" max="10"/>
-    <col width="20" customWidth="1" min="11" max="11"/>
-    <col width="20" customWidth="1" min="12" max="12"/>
-    <col width="9" customWidth="1" min="13" max="13"/>
-    <col width="9" customWidth="1" min="14" max="14"/>
-    <col width="9" customWidth="1" min="15" max="15"/>
-    <col width="9" customWidth="1" min="16" max="16"/>
-    <col width="18" customWidth="1" min="17" max="17"/>
-    <col width="56" customWidth="1" min="18" max="18"/>
+    <col width="10" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="9" max="9"/>
+    <col width="11" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="10" customWidth="1" min="12" max="12"/>
+    <col width="7" customWidth="1" min="13" max="13"/>
+    <col width="7" customWidth="1" min="14" max="14"/>
+    <col width="7" customWidth="1" min="15" max="15"/>
+    <col width="7" customWidth="1" min="16" max="16"/>
+    <col width="12" customWidth="1" min="17" max="17"/>
+    <col width="11" customWidth="1" min="18" max="18"/>
+    <col width="15" customWidth="1" min="19" max="19"/>
+    <col width="14" customWidth="1" min="20" max="20"/>
+    <col width="17" customWidth="1" min="21" max="21"/>
+    <col width="46" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>INVENTARIO DEL BANCO — DATOS DE EJEMPLO PARA DESARROLLO</t>
+          <t>INVENTARIO DEL BANCO - DATOS DE EJEMPLO PARA DESARROLLO</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NO son mediciones del banco real. Existen para construir y probar el motor de cobertura. La matriz de cobertura calculada desde este archivo es PROVISIONAL y no debe usarse para decidir el alcance.</t>
+          <t>NO son mediciones reales. La cobertura calculada desde aqui es PROVISIONAL. La plantilla vacia para el banco real es INVENTARIO-BANCO.xlsx</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>60 equipos · generado 2026-09-26 · fuente canónica: docs/inventario-demo.csv</t>
+          <t>72 equipos · generado 2026-09-26 · fuente canonica: docs/inventario-demo.csv</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="30" customHeight="1">
+    <row r="5" ht="28" customHeight="1">
       <c r="A5" s="3" t="inlineStr">
         <is>
-          <t>ID</t>
+          <t>id</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Marca</t>
+          <t>brand</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t>Modelo</t>
+          <t>model</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t>Variante / Región</t>
+          <t>region</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t>SoC fabricante</t>
+          <t>soc_vendor</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t>SoC modelo</t>
+          <t>soc_model</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>Plataforma</t>
+          <t>platform</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t>Mecanismo accesible</t>
+          <t>mechanism</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>Requiere auth / token</t>
+          <t>requires_auth</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t>Bootloader</t>
+          <t>bootloader</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t>Estado del equipo</t>
+          <t>condition</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t>Nivel máx. alcanzable</t>
+          <t>max_level</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t>T1</t>
+          <t>t1</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t>T2</t>
+          <t>t2</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t>T3</t>
+          <t>t3</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t>T4</t>
+          <t>t4</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t>Ubicación en banco</t>
+          <t>carrier</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t>Notas</t>
+          <t>carrier_lock</t>
+        </is>
+      </c>
+      <c r="S5" s="3" t="inlineStr">
+        <is>
+          <t>unlock_path</t>
+        </is>
+      </c>
+      <c r="T5" s="3" t="inlineStr">
+        <is>
+          <t>sim</t>
+        </is>
+      </c>
+      <c r="U5" s="3" t="inlineStr">
+        <is>
+          <t>bench_location</t>
+        </is>
+      </c>
+      <c r="V5" s="3" t="inlineStr">
+        <is>
+          <t>notes</t>
         </is>
       </c>
     </row>
@@ -627,7 +635,7 @@
       </c>
       <c r="D6" s="4" t="inlineStr">
         <is>
-          <t>SM-A035M / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E6" s="4" t="inlineStr">
@@ -642,62 +650,78 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>bootloop</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M6" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O6" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="P6" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q6" s="4" t="inlineStr">
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q6" s="4" t="inlineStr"/>
+      <c r="R6" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S6" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T6" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U6" s="4" t="inlineStr">
         <is>
           <t>Estante A</t>
         </is>
       </c>
-      <c r="R6" s="4" t="inlineStr">
-        <is>
-          <t>Caso tipico de bootloop resuelto con reflasheo</t>
+      <c r="V6" s="4" t="inlineStr">
+        <is>
+          <t>Caso tipico de bootloop</t>
         </is>
       </c>
     </row>
@@ -719,77 +743,93 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>SM-A135M / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Exynos</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>MT6769 Helio G80</t>
+          <t>Exynos 850</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>eub_exynos</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K7" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>bootloop</t>
         </is>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>
-          <t>L6 baseband</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="M7" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O7" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="P7" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q7" s="4" t="inlineStr">
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q7" s="4" t="inlineStr"/>
+      <c r="R7" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S7" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T7" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U7" s="4" t="inlineStr">
         <is>
           <t>Estante A</t>
         </is>
       </c>
-      <c r="R7" s="4" t="inlineStr">
-        <is>
-          <t>Control de identidad del banco</t>
+      <c r="V7" s="4" t="inlineStr">
+        <is>
+          <t>SM-A135M lleva Exynos, no Helio</t>
         </is>
       </c>
     </row>
@@ -806,82 +846,102 @@
       </c>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Galaxy A23</t>
+          <t>Galaxy A14 5G</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>SM-A235M / LATAM</t>
+          <t>US-METRO</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>SM6225 Snapdragon 680</t>
+          <t>MT6833 Dimensity 700</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>EDL 9008 + Sahara (QC)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K8" s="4" t="inlineStr">
         <is>
-          <t>No enciende</t>
+          <t>noboot</t>
         </is>
       </c>
       <c r="L8" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M8" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N8" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="Q8" s="4" t="inlineStr">
         <is>
-          <t>Estante A</t>
+          <t>metro</t>
         </is>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
-          <t>Programador firehose firmado disponible</t>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S8" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T8" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U8" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V8" s="4" t="inlineStr">
+        <is>
+          <t>Importado de EEUU, bloqueado a Metro</t>
         </is>
       </c>
     </row>
@@ -898,82 +958,102 @@
       </c>
       <c r="C9" s="4" t="inlineStr">
         <is>
-          <t>Galaxy A33 5G</t>
+          <t>Galaxy A15 5G</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>SM-A336M / LATAM</t>
+          <t>US-CRICKET</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Exynos</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Exynos 1280</t>
+          <t>MT6835 Dimensity 6100+</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>EUB (Exynos)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K9" s="4" t="inlineStr">
         <is>
-          <t>No enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L9" s="4" t="inlineStr">
         <is>
-          <t>L2 handshake</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M9" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N9" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="Q9" s="4" t="inlineStr">
         <is>
-          <t>Estante B</t>
+          <t>cricket</t>
         </is>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
-          <t>Requiere token de fabricante para escritura</t>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S9" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T9" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U9" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V9" s="4" t="inlineStr">
+        <is>
+          <t>Prepago bloqueado</t>
         </is>
       </c>
     </row>
@@ -990,84 +1070,96 @@
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Galaxy A53 5G</t>
+          <t>Galaxy A23</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>SM-A536M / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Exynos</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Exynos 1280</t>
+          <t>SM6225 Snapdragon 680</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>EUB (Exynos)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>own</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K10" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>noboot</t>
         </is>
       </c>
       <c r="L10" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M10" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N10" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t>Estante B</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q10" s="4" t="inlineStr"/>
       <c r="R10" s="4" t="inlineStr">
         <is>
-          <t>Solo lectura y diagnostico con el material actual</t>
-        </is>
-      </c>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S10" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T10" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U10" s="4" t="inlineStr">
+        <is>
+          <t>Estante A</t>
+        </is>
+      </c>
+      <c r="V10" s="4" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="4" t="inlineStr">
@@ -1082,12 +1174,12 @@
       </c>
       <c r="C11" s="4" t="inlineStr">
         <is>
-          <t>Galaxy M33 5G</t>
+          <t>Galaxy A33 5G</t>
         </is>
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>SM-M336B / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -1102,60 +1194,80 @@
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>EUB (Exynos)</t>
+          <t>eub_exynos</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
-          <t>Desconocido</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K11" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>noboot</t>
         </is>
       </c>
       <c r="L11" s="4" t="inlineStr">
         <is>
-          <t>L2 handshake</t>
+          <t>L2</t>
         </is>
       </c>
       <c r="M11" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N11" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q11" s="4" t="inlineStr">
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q11" s="4" t="inlineStr"/>
+      <c r="R11" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S11" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T11" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U11" s="4" t="inlineStr">
         <is>
           <t>Estante B</t>
         </is>
       </c>
-      <c r="R11" s="4" t="inlineStr"/>
+      <c r="V11" s="4" t="inlineStr">
+        <is>
+          <t>Requiere token de fabricante</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="4" t="inlineStr">
@@ -1170,84 +1282,96 @@
       </c>
       <c r="C12" s="4" t="inlineStr">
         <is>
-          <t>Galaxy S21 FE</t>
+          <t>Galaxy A53 5G</t>
         </is>
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>SM-G990E / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Exynos</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>SM8350 Snapdragon 888</t>
+          <t>Exynos 1280</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>EDL 9008 + Sahara (QC)</t>
+          <t>eub_exynos</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L12" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M12" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N12" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q12" s="4" t="inlineStr">
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q12" s="4" t="inlineStr"/>
+      <c r="R12" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S12" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T12" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U12" s="4" t="inlineStr">
         <is>
           <t>Estante B</t>
         </is>
       </c>
-      <c r="R12" s="4" t="inlineStr">
-        <is>
-          <t>EDL autenticado en SoC reciente</t>
-        </is>
-      </c>
+      <c r="V12" s="4" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="4" t="inlineStr">
@@ -1262,84 +1386,96 @@
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Galaxy S22 Ultra</t>
+          <t>Galaxy A54 5G</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>SM-S908E / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>Exynos</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>SM8450 Snapdragon 8 Gen 1</t>
+          <t>Exynos 1380</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>Fastboot</t>
+          <t>eub_exynos</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K13" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L13" s="4" t="inlineStr">
         <is>
-          <t>L6 baseband</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M13" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N13" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q13" s="4" t="inlineStr">
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q13" s="4" t="inlineStr"/>
+      <c r="R13" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S13" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T13" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U13" s="4" t="inlineStr">
         <is>
           <t>Estante B</t>
         </is>
       </c>
-      <c r="R13" s="4" t="inlineStr">
-        <is>
-          <t>Fastboot operativo, sin escritura EDL</t>
-        </is>
-      </c>
+      <c r="V13" s="4" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="4" t="inlineStr">
@@ -1354,12 +1490,12 @@
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>Galaxy Tab A7</t>
+          <t>Galaxy S21</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>SM-T500 / LATAM</t>
+          <t>US-VERIZON</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
@@ -1369,67 +1505,87 @@
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>SM6115 Snapdragon 662</t>
+          <t>SM8350 Snapdragon 888</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>EDL 9008 + Sahara (QC)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K14" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L14" s="4" t="inlineStr">
         <is>
-          <t>L5 board ID</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="M14" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N14" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="Q14" s="4" t="inlineStr">
         <is>
-          <t>Estante C</t>
+          <t>verizon</t>
         </is>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
-          <t>Tablet: mismo stack, mas volumen</t>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S14" s="4" t="inlineStr">
+        <is>
+          <t>carrier_automatic</t>
+        </is>
+      </c>
+      <c r="T14" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U14" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V14" s="4" t="inlineStr">
+        <is>
+          <t>Verizon libera automatico a los 60 dias</t>
         </is>
       </c>
     </row>
@@ -1441,89 +1597,105 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>Redmi 9A</t>
+          <t>Galaxy S21 Ultra</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>M2006C3LG / Global</t>
+          <t>US-ATT</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>MT6762 Helio G25</t>
+          <t>SM8350 Snapdragon 888</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
         <is>
-          <t>No enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L15" s="4" t="inlineStr">
         <is>
-          <t>L3 GPT</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M15" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N15" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="Q15" s="4" t="inlineStr">
         <is>
-          <t>Hub 1</t>
+          <t>att</t>
         </is>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
-          <t>DAA/SLA presente: requiere auth file legitimo</t>
-        </is>
-      </c>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S15" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T15" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U15" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V15" s="4" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="4" t="inlineStr">
@@ -1533,89 +1705,101 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>Redmi 9C</t>
+          <t>Galaxy S22 Ultra</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>M2006C3MG / Global</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>MT6765 Helio G35</t>
+          <t>SM8450 Snapdragon 8 Gen 1</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H16" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K16" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L16" s="4" t="inlineStr">
         <is>
-          <t>L3 GPT</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="M16" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N16" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q16" s="4" t="inlineStr">
-        <is>
-          <t>Hub 1</t>
-        </is>
-      </c>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q16" s="4" t="inlineStr"/>
       <c r="R16" s="4" t="inlineStr">
         <is>
-          <t>Variante con autenticacion en BROM</t>
-        </is>
-      </c>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S16" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T16" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U16" s="4" t="inlineStr">
+        <is>
+          <t>Estante B</t>
+        </is>
+      </c>
+      <c r="V16" s="4" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="4" t="inlineStr">
@@ -1625,17 +1809,17 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>Redmi Note 11</t>
+          <t>Galaxy S23</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>2201117TG / Global</t>
+          <t>US-TMOBILE</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
@@ -1645,69 +1829,85 @@
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>SM6225 Snapdragon 680</t>
+          <t>SM8550 Snapdragon 8 Gen 2</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>EDL 9008 + Sahara (QC)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K17" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L17" s="4" t="inlineStr">
         <is>
-          <t>L6 baseband</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M17" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N17" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="Q17" s="4" t="inlineStr">
         <is>
-          <t>Hub 1</t>
+          <t>tmobile</t>
         </is>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
-          <t>Existe variante MTK del mismo modelo: conflicto de identidad a vigilar</t>
-        </is>
-      </c>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S17" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T17" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U17" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V17" s="4" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="4" t="inlineStr">
@@ -1717,89 +1917,105 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>Redmi Note 11 (MTK)</t>
+          <t>Galaxy S23 Ultra</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>2201117TY / Global</t>
+          <t>US-ATT</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>MT6781 Helio G96</t>
+          <t>SM8550 Snapdragon 8 Gen 2</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H18" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K18" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L18" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="M18" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N18" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="Q18" s="4" t="inlineStr">
         <is>
-          <t>Hub 1</t>
+          <t>att</t>
         </is>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
-          <t>Misma familia, SoC distinto: la huella debe discriminar</t>
-        </is>
-      </c>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S18" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T18" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U18" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V18" s="4" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="4" t="inlineStr">
@@ -1809,17 +2025,17 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>Redmi Note 10</t>
+          <t>Galaxy S24 Ultra</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>M2101K7AG / Global</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
@@ -1829,65 +2045,81 @@
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>SM6150 Snapdragon 678</t>
+          <t>SM8650 Snapdragon 8 Gen 3</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
         <is>
-          <t>EDL 9008 + Sahara (QC)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K19" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L19" s="4" t="inlineStr">
         <is>
-          <t>L5 board ID</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="M19" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N19" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q19" s="4" t="inlineStr">
-        <is>
-          <t>Hub 1</t>
-        </is>
-      </c>
-      <c r="R19" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q19" s="4" t="inlineStr"/>
+      <c r="R19" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S19" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T19" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U19" s="4" t="inlineStr">
+        <is>
+          <t>Estante B</t>
+        </is>
+      </c>
+      <c r="V19" s="4" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="4" t="inlineStr">
@@ -1897,17 +2129,17 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
         <is>
-          <t>Poco X3 NFC</t>
+          <t>Galaxy Tab A7</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>M2007J20CG / Global</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1917,67 +2149,83 @@
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>SM7150 Snapdragon 732G</t>
+          <t>SM6115 Snapdragon 662</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
         <is>
-          <t>EDL 9008 + Sahara (QC)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>own</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K20" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
-          <t>L6 baseband</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="M20" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N20" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q20" s="4" t="inlineStr">
-        <is>
-          <t>Hub 1</t>
-        </is>
-      </c>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q20" s="4" t="inlineStr"/>
       <c r="R20" s="4" t="inlineStr">
         <is>
-          <t>Recuperacion de datos viable: userdata sin cifrar</t>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S20" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T20" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U20" s="4" t="inlineStr">
+        <is>
+          <t>Estante C</t>
+        </is>
+      </c>
+      <c r="V20" s="4" t="inlineStr">
+        <is>
+          <t>Tablet</t>
         </is>
       </c>
     </row>
@@ -1989,89 +2237,105 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Samsung</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
         <is>
-          <t>Poco F3</t>
+          <t>Galaxy A03s</t>
         </is>
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>M2012K11AG / Global</t>
+          <t>US-BOOST</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>SM8250 Snapdragon 870</t>
+          <t>MT6765 Helio P35</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H21" s="4" t="inlineStr">
         <is>
-          <t>Fastboot</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I21" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K21" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>bootloop</t>
         </is>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
-          <t>L6 baseband</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N21" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>no</t>
         </is>
       </c>
       <c r="Q21" s="4" t="inlineStr">
         <is>
-          <t>Hub 2</t>
+          <t>boost</t>
         </is>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
-          <t>Fastboot con bootloader desbloqueado</t>
-        </is>
-      </c>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S21" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T21" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U21" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V21" s="4" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="4" t="inlineStr">
@@ -2086,12 +2350,12 @@
       </c>
       <c r="C22" s="4" t="inlineStr">
         <is>
-          <t>Redmi Pad</t>
+          <t>Redmi 9A</t>
         </is>
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>22081283G / Global</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -2101,67 +2365,83 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>MT8781 Helio G99</t>
+          <t>MT6762 Helio G25</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H22" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I22" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K22" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>noboot</t>
         </is>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N22" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q22" s="4" t="inlineStr">
-        <is>
-          <t>Hub 2</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q22" s="4" t="inlineStr"/>
       <c r="R22" s="4" t="inlineStr">
         <is>
-          <t>Tablet</t>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S22" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T22" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U22" s="4" t="inlineStr">
+        <is>
+          <t>Hub 1</t>
+        </is>
+      </c>
+      <c r="V22" s="4" t="inlineStr">
+        <is>
+          <t>DAA/SLA presente</t>
         </is>
       </c>
     </row>
@@ -2178,12 +2458,12 @@
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>Redmi 12C</t>
+          <t>Redmi 9C</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>22120RN86G / Global</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
@@ -2193,65 +2473,81 @@
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>MT6769Z Helio G85</t>
+          <t>MT6765 Helio G35</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H23" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I23" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K23" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>bootloop</t>
         </is>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
-          <t>L3 GPT</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N23" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q23" s="4" t="inlineStr">
-        <is>
-          <t>Hub 2</t>
-        </is>
-      </c>
-      <c r="R23" s="4" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q23" s="4" t="inlineStr"/>
+      <c r="R23" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S23" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T23" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>Hub 1</t>
+        </is>
+      </c>
+      <c r="V23" s="4" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="4" t="inlineStr">
@@ -2261,17 +2557,17 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>Moto G31</t>
+          <t>Redmi 12 4G</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>XT2173-1 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
@@ -2281,69 +2577,81 @@
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>MT6769V Helio G85</t>
+          <t>MT6769H Helio G88</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>bootloop</t>
         </is>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
-          <t>L6 baseband</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N24" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q24" s="4" t="inlineStr">
-        <is>
-          <t>Estante A</t>
-        </is>
-      </c>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q24" s="4" t="inlineStr"/>
       <c r="R24" s="4" t="inlineStr">
         <is>
-          <t>Referencia de identidad y backup</t>
-        </is>
-      </c>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S24" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T24" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U24" s="4" t="inlineStr">
+        <is>
+          <t>Hub 1</t>
+        </is>
+      </c>
+      <c r="V24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="4" t="inlineStr">
@@ -2353,85 +2661,101 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
         <is>
-          <t>Moto G42</t>
+          <t>Redmi 12C</t>
         </is>
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>XT2233-1 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>SM6225 Snapdragon 680</t>
+          <t>MT6769Z Helio G85</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H25" s="4" t="inlineStr">
         <is>
-          <t>EDL 9008 + Sahara (QC)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I25" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K25" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
-          <t>L5 board ID</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N25" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q25" s="4" t="inlineStr">
-        <is>
-          <t>Estante A</t>
-        </is>
-      </c>
-      <c r="R25" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q25" s="4" t="inlineStr"/>
+      <c r="R25" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S25" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T25" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U25" s="4" t="inlineStr">
+        <is>
+          <t>Hub 2</t>
+        </is>
+      </c>
+      <c r="V25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="4" t="inlineStr">
@@ -2441,17 +2765,17 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
         <is>
-          <t>Moto E22</t>
+          <t>Redmi 13C</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>XT2229-1 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2461,65 +2785,81 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>MT6765 Helio G37</t>
+          <t>MT6769Z Helio G85</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H26" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I26" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K26" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
-          <t>L5 board ID</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="M26" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N26" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q26" s="4" t="inlineStr">
-        <is>
-          <t>Estante A</t>
-        </is>
-      </c>
-      <c r="R26" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q26" s="4" t="inlineStr"/>
+      <c r="R26" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S26" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T26" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U26" s="4" t="inlineStr">
+        <is>
+          <t>Hub 2</t>
+        </is>
+      </c>
+      <c r="V26" s="4" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="4" t="inlineStr">
@@ -2529,17 +2869,17 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
         <is>
-          <t>Moto G52</t>
+          <t>Redmi Note 10</t>
         </is>
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>XT2221-1 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2549,65 +2889,81 @@
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>SM6225-AD Snapdragon 680</t>
+          <t>SM6150 Snapdragon 678</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H27" s="4" t="inlineStr">
         <is>
-          <t>EDL 9008 + Sahara (QC)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I27" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>own</t>
         </is>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K27" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
-          <t>L6 baseband</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N27" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q27" s="4" t="inlineStr">
-        <is>
-          <t>Estante A</t>
-        </is>
-      </c>
-      <c r="R27" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q27" s="4" t="inlineStr"/>
+      <c r="R27" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S27" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T27" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U27" s="4" t="inlineStr">
+        <is>
+          <t>Hub 1</t>
+        </is>
+      </c>
+      <c r="V27" s="4" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="4" t="inlineStr">
@@ -2617,17 +2973,17 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
         <is>
-          <t>Moto G71 5G</t>
+          <t>Redmi Note 11 QC</t>
         </is>
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>XT2169-1 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -2637,65 +2993,85 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>SM6375 Snapdragon 695</t>
+          <t>SM6225 Snapdragon 680</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H28" s="4" t="inlineStr">
         <is>
-          <t>EDL 9008 + Sahara (QC)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I28" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>own</t>
         </is>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K28" s="4" t="inlineStr">
         <is>
-          <t>No enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
-          <t>L3 GPT</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N28" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q28" s="4" t="inlineStr">
-        <is>
-          <t>Estante B</t>
-        </is>
-      </c>
-      <c r="R28" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q28" s="4" t="inlineStr"/>
+      <c r="R28" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S28" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T28" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U28" s="4" t="inlineStr">
+        <is>
+          <t>Hub 1</t>
+        </is>
+      </c>
+      <c r="V28" s="4" t="inlineStr">
+        <is>
+          <t>Existe variante MTK con el mismo nombre</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="4" t="inlineStr">
@@ -2705,85 +3081,101 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>Tecno</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
         <is>
-          <t>Spark 8C</t>
+          <t>Redmi Note 11 MTK</t>
         </is>
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>KG5j / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Unisoc</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>T606</t>
+          <t>MT6781 Helio G96</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H29" s="4" t="inlineStr">
         <is>
-          <t>FDL (Unisoc)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I29" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K29" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>bootloop</t>
         </is>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
-          <t>L3 GPT</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N29" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q29" s="4" t="inlineStr">
-        <is>
-          <t>Caja pendientes</t>
-        </is>
-      </c>
-      <c r="R29" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q29" s="4" t="inlineStr"/>
+      <c r="R29" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S29" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T29" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U29" s="4" t="inlineStr">
+        <is>
+          <t>Hub 1</t>
+        </is>
+      </c>
+      <c r="V29" s="4" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="4" t="inlineStr">
@@ -2793,85 +3185,101 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>Tecno</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
         <is>
-          <t>Spark Go 2022</t>
+          <t>Redmi Note 12 4G</t>
         </is>
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>KG5 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Unisoc</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>SC9863A</t>
+          <t>SM6225 Snapdragon 685</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>FDL (Unisoc)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>own</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
         <is>
-          <t>No enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
-          <t>L2 handshake</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N30" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q30" s="4" t="inlineStr">
-        <is>
-          <t>Caja pendientes</t>
-        </is>
-      </c>
-      <c r="R30" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q30" s="4" t="inlineStr"/>
+      <c r="R30" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S30" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T30" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U30" s="4" t="inlineStr">
+        <is>
+          <t>Hub 2</t>
+        </is>
+      </c>
+      <c r="V30" s="4" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="4" t="inlineStr">
@@ -2881,85 +3289,101 @@
       </c>
       <c r="B31" s="4" t="inlineStr">
         <is>
-          <t>Tecno</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="C31" s="4" t="inlineStr">
         <is>
-          <t>Camon 19</t>
+          <t>Redmi Note 13 4G</t>
         </is>
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>CI6n / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>MT6789 Helio G85</t>
+          <t>SM6225 Snapdragon 685</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H31" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I31" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>own</t>
         </is>
       </c>
       <c r="J31" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K31" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L31" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="M31" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N31" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q31" s="4" t="inlineStr">
-        <is>
-          <t>Caja pendientes</t>
-        </is>
-      </c>
-      <c r="R31" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q31" s="4" t="inlineStr"/>
+      <c r="R31" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S31" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T31" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U31" s="4" t="inlineStr">
+        <is>
+          <t>Hub 2</t>
+        </is>
+      </c>
+      <c r="V31" s="4" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="4" t="inlineStr">
@@ -2969,85 +3393,105 @@
       </c>
       <c r="B32" s="4" t="inlineStr">
         <is>
-          <t>Tecno</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
         <is>
-          <t>Pova 4</t>
+          <t>POCO X3 NFC</t>
         </is>
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>LG7n / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>MT8781 Helio G99</t>
+          <t>SM7150 Snapdragon 732G</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H32" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I32" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>own</t>
         </is>
       </c>
       <c r="J32" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K32" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L32" s="4" t="inlineStr">
         <is>
-          <t>L3 GPT</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="M32" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N32" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="inlineStr">
-        <is>
-          <t>Caja pendientes</t>
-        </is>
-      </c>
-      <c r="R32" s="4" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q32" s="4" t="inlineStr"/>
+      <c r="R32" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S32" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T32" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U32" s="4" t="inlineStr">
+        <is>
+          <t>Hub 1</t>
+        </is>
+      </c>
+      <c r="V32" s="4" t="inlineStr">
+        <is>
+          <t>Recuperacion de datos viable</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
@@ -3057,85 +3501,105 @@
       </c>
       <c r="B33" s="4" t="inlineStr">
         <is>
-          <t>Infinix</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
         <is>
-          <t>Hot 12</t>
+          <t>POCO F3</t>
         </is>
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>X6817 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>MT6769 Helio G85</t>
+          <t>SM8250 Snapdragon 870</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H33" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I33" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>own</t>
         </is>
       </c>
       <c r="J33" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K33" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L33" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="M33" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N33" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q33" s="4" t="inlineStr">
-        <is>
-          <t>Caja pendientes</t>
-        </is>
-      </c>
-      <c r="R33" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q33" s="4" t="inlineStr"/>
+      <c r="R33" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S33" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T33" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U33" s="4" t="inlineStr">
+        <is>
+          <t>Hub 2</t>
+        </is>
+      </c>
+      <c r="V33" s="4" t="inlineStr">
+        <is>
+          <t>Fastboot con bootloader abierto</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="4" t="inlineStr">
@@ -3145,85 +3609,105 @@
       </c>
       <c r="B34" s="4" t="inlineStr">
         <is>
-          <t>Infinix</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
         <is>
-          <t>Smart 6</t>
+          <t>Redmi Pad</t>
         </is>
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>X6511 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Unisoc</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>SC9863A</t>
+          <t>MT8781 Helio G99</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H34" s="4" t="inlineStr">
         <is>
-          <t>FDL (Unisoc)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I34" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J34" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K34" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L34" s="4" t="inlineStr">
         <is>
-          <t>L3 GPT</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M34" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N34" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="inlineStr">
-        <is>
-          <t>Caja pendientes</t>
-        </is>
-      </c>
-      <c r="R34" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q34" s="4" t="inlineStr"/>
+      <c r="R34" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S34" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T34" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U34" s="4" t="inlineStr">
+        <is>
+          <t>Hub 2</t>
+        </is>
+      </c>
+      <c r="V34" s="4" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
@@ -3233,17 +3717,17 @@
       </c>
       <c r="B35" s="4" t="inlineStr">
         <is>
-          <t>Infinix</t>
+          <t>Xiaomi</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
         <is>
-          <t>Note 12</t>
+          <t>Redmi A2</t>
         </is>
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>X663 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
@@ -3253,65 +3737,85 @@
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>MT6789 Helio G96</t>
+          <t>MT6765 Helio G36</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H35" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I35" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J35" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K35" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>noboot</t>
         </is>
       </c>
       <c r="L35" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="M35" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N35" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="inlineStr">
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q35" s="4" t="inlineStr"/>
+      <c r="R35" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S35" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T35" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U35" s="4" t="inlineStr">
         <is>
           <t>Caja pendientes</t>
         </is>
       </c>
-      <c r="R35" s="4" t="inlineStr"/>
+      <c r="V35" s="4" t="inlineStr">
+        <is>
+          <t>Gama de entrada</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="4" t="inlineStr">
@@ -3321,17 +3825,17 @@
       </c>
       <c r="B36" s="4" t="inlineStr">
         <is>
-          <t>itel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
         <is>
-          <t>A48</t>
+          <t>Moto E13</t>
         </is>
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>A48 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
@@ -3341,65 +3845,81 @@
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>SC9863A</t>
+          <t>T606</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H36" s="4" t="inlineStr">
         <is>
-          <t>FDL (Unisoc)</t>
+          <t>fdl_unisoc</t>
         </is>
       </c>
       <c r="I36" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J36" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K36" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L36" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M36" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N36" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q36" s="4" t="inlineStr">
-        <is>
-          <t>Caja pendientes</t>
-        </is>
-      </c>
-      <c r="R36" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q36" s="4" t="inlineStr"/>
+      <c r="R36" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S36" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T36" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U36" s="4" t="inlineStr">
+        <is>
+          <t>Estante A</t>
+        </is>
+      </c>
+      <c r="V36" s="4" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="4" t="inlineStr">
@@ -3409,85 +3929,105 @@
       </c>
       <c r="B37" s="4" t="inlineStr">
         <is>
-          <t>itel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
         <is>
-          <t>A58</t>
+          <t>Moto G31</t>
         </is>
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>A58 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Unisoc</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>SC9863A</t>
+          <t>MT6769V Helio G85</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H37" s="4" t="inlineStr">
         <is>
-          <t>FDL (Unisoc)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I37" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J37" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K37" s="4" t="inlineStr">
         <is>
-          <t>No enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L37" s="4" t="inlineStr">
         <is>
-          <t>L3 GPT</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="M37" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N37" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q37" s="4" t="inlineStr">
-        <is>
-          <t>Caja pendientes</t>
-        </is>
-      </c>
-      <c r="R37" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q37" s="4" t="inlineStr"/>
+      <c r="R37" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S37" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T37" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U37" s="4" t="inlineStr">
+        <is>
+          <t>Estante A</t>
+        </is>
+      </c>
+      <c r="V37" s="4" t="inlineStr">
+        <is>
+          <t>Referencia de identidad y backup</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="4" t="inlineStr">
@@ -3497,85 +4037,101 @@
       </c>
       <c r="B38" s="4" t="inlineStr">
         <is>
-          <t>itel</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
         <is>
-          <t>Vision 3</t>
+          <t>Moto G42</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Vision3 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Unisoc</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>T310</t>
+          <t>SM6225 Snapdragon 680</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H38" s="4" t="inlineStr">
         <is>
-          <t>FDL (Unisoc)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I38" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>own</t>
         </is>
       </c>
       <c r="J38" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K38" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>bootloop</t>
         </is>
       </c>
       <c r="L38" s="4" t="inlineStr">
         <is>
-          <t>L3 GPT</t>
+          <t>L5</t>
         </is>
       </c>
       <c r="M38" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N38" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q38" s="4" t="inlineStr">
-        <is>
-          <t>Caja pendientes</t>
-        </is>
-      </c>
-      <c r="R38" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q38" s="4" t="inlineStr"/>
+      <c r="R38" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S38" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T38" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U38" s="4" t="inlineStr">
+        <is>
+          <t>Estante A</t>
+        </is>
+      </c>
+      <c r="V38" s="4" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="4" t="inlineStr">
@@ -3585,85 +4141,101 @@
       </c>
       <c r="B39" s="4" t="inlineStr">
         <is>
-          <t>ZTE</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
         <is>
-          <t>Blade A51</t>
+          <t>Moto G52</t>
         </is>
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>A51 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Unisoc</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>SC9863A</t>
+          <t>SM6225 Snapdragon 680</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H39" s="4" t="inlineStr">
         <is>
-          <t>FDL (Unisoc)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I39" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>own</t>
         </is>
       </c>
       <c r="J39" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K39" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L39" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="M39" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N39" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q39" s="4" t="inlineStr">
-        <is>
-          <t>Estante C</t>
-        </is>
-      </c>
-      <c r="R39" s="4" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q39" s="4" t="inlineStr"/>
+      <c r="R39" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S39" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T39" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U39" s="4" t="inlineStr">
+        <is>
+          <t>Estante A</t>
+        </is>
+      </c>
+      <c r="V39" s="4" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="4" t="inlineStr">
@@ -3673,85 +4245,101 @@
       </c>
       <c r="B40" s="4" t="inlineStr">
         <is>
-          <t>ZTE</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
         <is>
-          <t>Blade A31</t>
+          <t>Moto G71 5G</t>
         </is>
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>A31 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Unisoc</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>SC9832E</t>
+          <t>SM6375 Snapdragon 695</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H40" s="4" t="inlineStr">
         <is>
-          <t>FDL (Unisoc)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I40" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J40" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K40" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>noboot</t>
         </is>
       </c>
       <c r="L40" s="4" t="inlineStr">
         <is>
-          <t>L3 GPT</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="M40" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N40" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q40" s="4" t="inlineStr">
-        <is>
-          <t>Estante C</t>
-        </is>
-      </c>
-      <c r="R40" s="4" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q40" s="4" t="inlineStr"/>
+      <c r="R40" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S40" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T40" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U40" s="4" t="inlineStr">
+        <is>
+          <t>Estante B</t>
+        </is>
+      </c>
+      <c r="V40" s="4" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="4" t="inlineStr">
@@ -3761,17 +4349,17 @@
       </c>
       <c r="B41" s="4" t="inlineStr">
         <is>
-          <t>ZTE</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
         <is>
-          <t>Blade V40</t>
+          <t>Moto G84 5G</t>
         </is>
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>V40 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
@@ -3781,65 +4369,81 @@
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>SM6225 Snapdragon 680</t>
+          <t>SM6375 Snapdragon 695</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H41" s="4" t="inlineStr">
         <is>
-          <t>EDL 9008 + Sahara (QC)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I41" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J41" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K41" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L41" s="4" t="inlineStr">
         <is>
-          <t>L5 board ID</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M41" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N41" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="inlineStr">
-        <is>
-          <t>Estante C</t>
-        </is>
-      </c>
-      <c r="R41" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q41" s="4" t="inlineStr"/>
+      <c r="R41" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S41" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T41" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U41" s="4" t="inlineStr">
+        <is>
+          <t>Estante B</t>
+        </is>
+      </c>
+      <c r="V41" s="4" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="4" t="inlineStr">
@@ -3849,17 +4453,17 @@
       </c>
       <c r="B42" s="4" t="inlineStr">
         <is>
-          <t>OPPO</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
         <is>
-          <t>A16</t>
+          <t>Moto G Pure</t>
         </is>
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>CPH2269 / LATAM</t>
+          <t>US-CRICKET</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
@@ -3869,65 +4473,89 @@
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>MT6765 Helio G35</t>
+          <t>MT6765 Helio G25</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H42" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I42" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J42" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K42" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>bootloop</t>
         </is>
       </c>
       <c r="L42" s="4" t="inlineStr">
         <is>
-          <t>L3 GPT</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="M42" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N42" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="Q42" s="4" t="inlineStr">
         <is>
-          <t>Hub 2</t>
-        </is>
-      </c>
-      <c r="R42" s="4" t="inlineStr"/>
+          <t>cricket</t>
+        </is>
+      </c>
+      <c r="R42" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S42" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T42" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U42" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V42" s="4" t="inlineStr">
+        <is>
+          <t>Prepago bloqueado</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="4" t="inlineStr">
@@ -3937,85 +4565,109 @@
       </c>
       <c r="B43" s="4" t="inlineStr">
         <is>
-          <t>OPPO</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
         <is>
-          <t>A57</t>
+          <t>Moto G Power 2022</t>
         </is>
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>CPH2387 / LATAM</t>
+          <t>US-VERIZON</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>SM6225 Snapdragon 680</t>
+          <t>MT6765H Helio G37</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H43" s="4" t="inlineStr">
         <is>
-          <t>EDL 9008 + Sahara (QC)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I43" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J43" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K43" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L43" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M43" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N43" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="Q43" s="4" t="inlineStr">
         <is>
-          <t>Hub 2</t>
-        </is>
-      </c>
-      <c r="R43" s="4" t="inlineStr"/>
+          <t>verizon</t>
+        </is>
+      </c>
+      <c r="R43" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S43" s="4" t="inlineStr">
+        <is>
+          <t>carrier_automatic</t>
+        </is>
+      </c>
+      <c r="T43" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U43" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V43" s="4" t="inlineStr">
+        <is>
+          <t>Elegible para liberacion automatica</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="4" t="inlineStr">
@@ -4025,85 +4677,105 @@
       </c>
       <c r="B44" s="4" t="inlineStr">
         <is>
-          <t>realme</t>
+          <t>Motorola</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
         <is>
-          <t>C31</t>
+          <t>Moto G Stylus 2023</t>
         </is>
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>RMX3501 / LATAM</t>
+          <t>US-UNLOCK</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Unisoc</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>T612</t>
+          <t>MT6769H Helio G88</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H44" s="4" t="inlineStr">
         <is>
-          <t>FDL (Unisoc)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I44" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J44" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K44" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L44" s="4" t="inlineStr">
         <is>
-          <t>L3 GPT</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M44" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N44" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="Q44" s="4" t="inlineStr">
         <is>
-          <t>Hub 2</t>
-        </is>
-      </c>
-      <c r="R44" s="4" t="inlineStr"/>
+          <t>att</t>
+        </is>
+      </c>
+      <c r="R44" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S44" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T44" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U44" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V44" s="4" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="4" t="inlineStr">
@@ -4113,85 +4785,101 @@
       </c>
       <c r="B45" s="4" t="inlineStr">
         <is>
-          <t>realme</t>
+          <t>Tecno</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
         <is>
-          <t>C35</t>
+          <t>Spark 8C</t>
         </is>
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>RMX3511 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Unisoc</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>MT6765 Helio G35</t>
+          <t>T606</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H45" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>fdl_unisoc</t>
         </is>
       </c>
       <c r="I45" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J45" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K45" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>bootloop</t>
         </is>
       </c>
       <c r="L45" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="M45" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N45" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q45" s="4" t="inlineStr">
-        <is>
-          <t>Hub 2</t>
-        </is>
-      </c>
-      <c r="R45" s="4" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q45" s="4" t="inlineStr"/>
+      <c r="R45" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S45" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T45" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U45" s="4" t="inlineStr">
+        <is>
+          <t>Caja pendientes</t>
+        </is>
+      </c>
+      <c r="V45" s="4" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="4" t="inlineStr">
@@ -4201,85 +4889,101 @@
       </c>
       <c r="B46" s="4" t="inlineStr">
         <is>
-          <t>vivo</t>
+          <t>Tecno</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
         <is>
-          <t>Y21</t>
+          <t>Spark 10</t>
         </is>
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>V2111 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Unisoc</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>MT6769 Helio G80</t>
+          <t>T606</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H46" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>fdl_unisoc</t>
         </is>
       </c>
       <c r="I46" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J46" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K46" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L46" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M46" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N46" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q46" s="4" t="inlineStr">
-        <is>
-          <t>Hub 2</t>
-        </is>
-      </c>
-      <c r="R46" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q46" s="4" t="inlineStr"/>
+      <c r="R46" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S46" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T46" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U46" s="4" t="inlineStr">
+        <is>
+          <t>Caja pendientes</t>
+        </is>
+      </c>
+      <c r="V46" s="4" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="4" t="inlineStr">
@@ -4289,17 +4993,17 @@
       </c>
       <c r="B47" s="4" t="inlineStr">
         <is>
-          <t>Honor</t>
+          <t>Tecno</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
         <is>
-          <t>X6</t>
+          <t>Camon 19</t>
         </is>
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>VNE-LX2 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
@@ -4309,65 +5013,81 @@
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>MT6765 Helio G25</t>
+          <t>MT6769Z Helio G85</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H47" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I47" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J47" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K47" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L47" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M47" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N47" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q47" s="4" t="inlineStr">
-        <is>
-          <t>Estante C</t>
-        </is>
-      </c>
-      <c r="R47" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q47" s="4" t="inlineStr"/>
+      <c r="R47" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S47" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T47" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U47" s="4" t="inlineStr">
+        <is>
+          <t>Caja pendientes</t>
+        </is>
+      </c>
+      <c r="V47" s="4" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="4" t="inlineStr">
@@ -4377,85 +5097,101 @@
       </c>
       <c r="B48" s="4" t="inlineStr">
         <is>
-          <t>Honor</t>
+          <t>Tecno</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
         <is>
-          <t>X7</t>
+          <t>Pova 4</t>
         </is>
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>CMA-LX2 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>SM6225 Snapdragon 680</t>
+          <t>MT8781 Helio G99</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H48" s="4" t="inlineStr">
         <is>
-          <t>EDL 9008 + Sahara (QC)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I48" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J48" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K48" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>bootloop</t>
         </is>
       </c>
       <c r="L48" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="M48" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N48" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q48" s="4" t="inlineStr">
-        <is>
-          <t>Estante C</t>
-        </is>
-      </c>
-      <c r="R48" s="4" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q48" s="4" t="inlineStr"/>
+      <c r="R48" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S48" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T48" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U48" s="4" t="inlineStr">
+        <is>
+          <t>Caja pendientes</t>
+        </is>
+      </c>
+      <c r="V48" s="4" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="4" t="inlineStr">
@@ -4465,89 +5201,101 @@
       </c>
       <c r="B49" s="4" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>Infinix</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
         <is>
-          <t>Y6p</t>
+          <t>Hot 12</t>
         </is>
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>MED-LX9 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>HiSilicon</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Kirin 710A</t>
+          <t>MT6769 Helio G85</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H49" s="4" t="inlineStr">
         <is>
-          <t>Solo ADB</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I49" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J49" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K49" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L49" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M49" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N49" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q49" s="4" t="inlineStr">
-        <is>
-          <t>Estante C</t>
-        </is>
-      </c>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q49" s="4" t="inlineStr"/>
       <c r="R49" s="4" t="inlineStr">
         <is>
-          <t>Bootloader cerrado, sin ruta de escritura conocida</t>
-        </is>
-      </c>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S49" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T49" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U49" s="4" t="inlineStr">
+        <is>
+          <t>Caja pendientes</t>
+        </is>
+      </c>
+      <c r="V49" s="4" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="4" t="inlineStr">
@@ -4557,89 +5305,101 @@
       </c>
       <c r="B50" s="4" t="inlineStr">
         <is>
-          <t>Huawei</t>
+          <t>Infinix</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
         <is>
-          <t>Nova 9</t>
+          <t>Note 12</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>NAM-LX9 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Qualcomm</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>SM7325 Snapdragon 778G</t>
+          <t>MT6781 Helio G96</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr">
         <is>
-          <t>Solo ADB</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I50" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J50" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K50" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L50" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M50" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N50" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q50" s="4" t="inlineStr">
-        <is>
-          <t>Estante C</t>
-        </is>
-      </c>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q50" s="4" t="inlineStr"/>
       <c r="R50" s="4" t="inlineStr">
         <is>
-          <t>Sin desbloqueo oficial de bootloader</t>
-        </is>
-      </c>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S50" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T50" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U50" s="4" t="inlineStr">
+        <is>
+          <t>Caja pendientes</t>
+        </is>
+      </c>
+      <c r="V50" s="4" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="4" t="inlineStr">
@@ -4649,17 +5409,17 @@
       </c>
       <c r="B51" s="4" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>Infinix</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
         <is>
-          <t>C21</t>
+          <t>Smart 6</t>
         </is>
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>TA-1352 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
@@ -4674,60 +5434,76 @@
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr">
         <is>
-          <t>FDL (Unisoc)</t>
+          <t>fdl_unisoc</t>
         </is>
       </c>
       <c r="I51" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J51" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K51" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>bootloop</t>
         </is>
       </c>
       <c r="L51" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="M51" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N51" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q51" s="4" t="inlineStr">
-        <is>
-          <t>Estante C</t>
-        </is>
-      </c>
-      <c r="R51" s="4" t="inlineStr"/>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q51" s="4" t="inlineStr"/>
+      <c r="R51" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S51" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T51" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U51" s="4" t="inlineStr">
+        <is>
+          <t>Caja pendientes</t>
+        </is>
+      </c>
+      <c r="V51" s="4" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="4" t="inlineStr">
@@ -4737,17 +5513,17 @@
       </c>
       <c r="B52" s="4" t="inlineStr">
         <is>
-          <t>Nokia</t>
+          <t>itel</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
         <is>
-          <t>G21</t>
+          <t>A48</t>
         </is>
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>TA-1418 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
@@ -4757,65 +5533,81 @@
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>T606</t>
+          <t>SC9863A</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H52" s="4" t="inlineStr">
         <is>
-          <t>FDL (Unisoc)</t>
+          <t>fdl_unisoc</t>
         </is>
       </c>
       <c r="I52" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J52" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K52" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L52" s="4" t="inlineStr">
         <is>
-          <t>L3 GPT</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M52" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N52" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q52" s="4" t="inlineStr">
-        <is>
-          <t>Estante C</t>
-        </is>
-      </c>
-      <c r="R52" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q52" s="4" t="inlineStr"/>
+      <c r="R52" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S52" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T52" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U52" s="4" t="inlineStr">
+        <is>
+          <t>Caja pendientes</t>
+        </is>
+      </c>
+      <c r="V52" s="4" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="4" t="inlineStr">
@@ -4825,89 +5617,101 @@
       </c>
       <c r="B53" s="4" t="inlineStr">
         <is>
-          <t>Google</t>
+          <t>itel</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
         <is>
-          <t>Pixel 6</t>
+          <t>A58</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>GB7N6 / Global</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Google Tensor</t>
+          <t>Unisoc</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Tensor G1</t>
+          <t>SC9863A</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H53" s="4" t="inlineStr">
         <is>
-          <t>Fastboot</t>
+          <t>fdl_unisoc</t>
         </is>
       </c>
       <c r="I53" s="4" t="inlineStr">
         <is>
-          <t>Si - requiere tercero legitimo</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J53" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K53" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>noboot</t>
         </is>
       </c>
       <c r="L53" s="4" t="inlineStr">
         <is>
-          <t>L6 baseband</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="M53" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N53" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q53" s="4" t="inlineStr">
-        <is>
-          <t>Rack de caos</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q53" s="4" t="inlineStr"/>
       <c r="R53" s="4" t="inlineStr">
         <is>
-          <t>Acceso EDL restringido; solo fastboot firmado</t>
-        </is>
-      </c>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S53" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T53" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U53" s="4" t="inlineStr">
+        <is>
+          <t>Caja pendientes</t>
+        </is>
+      </c>
+      <c r="V53" s="4" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="4" t="inlineStr">
@@ -4917,89 +5721,101 @@
       </c>
       <c r="B54" s="4" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>itel</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
         <is>
-          <t>iPhone 8</t>
+          <t>Vision 3</t>
         </is>
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>A1905 / Global</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Unisoc</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>A11 Bionic</t>
+          <t>SC9863A</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H54" s="4" t="inlineStr">
         <is>
-          <t>DFU (Apple)</t>
+          <t>fdl_unisoc</t>
         </is>
       </c>
       <c r="I54" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J54" s="4" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K54" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>bootloop</t>
         </is>
       </c>
       <c r="L54" s="4" t="inlineStr">
         <is>
-          <t>L6 baseband</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="M54" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N54" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q54" s="4" t="inlineStr">
-        <is>
-          <t>Estante C</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q54" s="4" t="inlineStr"/>
       <c r="R54" s="4" t="inlineStr">
         <is>
-          <t>Restore solo a version firmada; sin downgrade</t>
-        </is>
-      </c>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S54" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T54" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U54" s="4" t="inlineStr">
+        <is>
+          <t>Caja pendientes</t>
+        </is>
+      </c>
+      <c r="V54" s="4" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="4" t="inlineStr">
@@ -5009,85 +5825,101 @@
       </c>
       <c r="B55" s="4" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>ZTE</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
         <is>
-          <t>iPhone XR</t>
+          <t>Blade A51</t>
         </is>
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>A2105 / Global</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Unisoc</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>A12 Bionic</t>
+          <t>SC9863A</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H55" s="4" t="inlineStr">
         <is>
-          <t>DFU (Apple)</t>
+          <t>fdl_unisoc</t>
         </is>
       </c>
       <c r="I55" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J55" s="4" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K55" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L55" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M55" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N55" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q55" s="4" t="inlineStr">
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q55" s="4" t="inlineStr"/>
+      <c r="R55" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S55" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T55" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U55" s="4" t="inlineStr">
         <is>
           <t>Estante C</t>
         </is>
       </c>
-      <c r="R55" s="4" t="inlineStr"/>
+      <c r="V55" s="4" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="4" t="inlineStr">
@@ -5097,89 +5929,101 @@
       </c>
       <c r="B56" s="4" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>ZTE</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
         <is>
-          <t>iPhone 11</t>
+          <t>Blade V40 Vita</t>
         </is>
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>A2221 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Unisoc</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>A13 Bionic</t>
+          <t>T606</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H56" s="4" t="inlineStr">
         <is>
-          <t>DFU (Apple)</t>
+          <t>fdl_unisoc</t>
         </is>
       </c>
       <c r="I56" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J56" s="4" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K56" s="4" t="inlineStr">
         <is>
-          <t>Solo recovery</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L56" s="4" t="inlineStr">
         <is>
-          <t>L5 board ID</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M56" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N56" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q56" s="4" t="inlineStr">
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q56" s="4" t="inlineStr"/>
+      <c r="R56" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S56" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T56" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U56" s="4" t="inlineStr">
         <is>
           <t>Estante C</t>
         </is>
       </c>
-      <c r="R56" s="4" t="inlineStr">
-        <is>
-          <t>Salida de recovery y restore firmado</t>
-        </is>
-      </c>
+      <c r="V56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="4" t="inlineStr">
@@ -5189,89 +6033,101 @@
       </c>
       <c r="B57" s="4" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>OPPO</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
         <is>
-          <t>iPhone 12</t>
+          <t>A16</t>
         </is>
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>A2402 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>MediaTek</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>A14 Bionic</t>
+          <t>MT6765 Helio G35</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H57" s="4" t="inlineStr">
         <is>
-          <t>DFU (Apple)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I57" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J57" s="4" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K57" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>bootloop</t>
         </is>
       </c>
       <c r="L57" s="4" t="inlineStr">
         <is>
-          <t>L6 baseband</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="M57" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N57" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="Q57" s="4" t="inlineStr">
-        <is>
-          <t>Estante C</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q57" s="4" t="inlineStr"/>
       <c r="R57" s="4" t="inlineStr">
         <is>
-          <t>Backup completo con credenciales del dueño</t>
-        </is>
-      </c>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S57" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T57" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U57" s="4" t="inlineStr">
+        <is>
+          <t>Hub 2</t>
+        </is>
+      </c>
+      <c r="V57" s="4" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
@@ -5281,85 +6137,101 @@
       </c>
       <c r="B58" s="4" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>OPPO</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
         <is>
-          <t>iPhone SE 2020</t>
+          <t>A57</t>
         </is>
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>A2296 / Global</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>A13 Bionic</t>
+          <t>SM6225 Snapdragon 680</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H58" s="4" t="inlineStr">
         <is>
-          <t>DFU (Apple)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I58" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J58" s="4" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K58" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L58" s="4" t="inlineStr">
         <is>
-          <t>L5 board ID</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M58" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N58" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q58" s="4" t="inlineStr">
-        <is>
-          <t>Estante C</t>
-        </is>
-      </c>
-      <c r="R58" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q58" s="4" t="inlineStr"/>
+      <c r="R58" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S58" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T58" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U58" s="4" t="inlineStr">
+        <is>
+          <t>Hub 2</t>
+        </is>
+      </c>
+      <c r="V58" s="4" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
@@ -5369,89 +6241,101 @@
       </c>
       <c r="B59" s="4" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>realme</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
         <is>
-          <t>iPad 9</t>
+          <t>C31</t>
         </is>
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>A2602 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Apple</t>
+          <t>Unisoc</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>A13 Bionic</t>
+          <t>T612</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
         <is>
-          <t>iOS</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H59" s="4" t="inlineStr">
         <is>
-          <t>DFU (Apple)</t>
+          <t>fdl_unisoc</t>
         </is>
       </c>
       <c r="I59" s="4" t="inlineStr">
         <is>
-          <t>Si - propio</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J59" s="4" t="inlineStr">
         <is>
-          <t>No aplica</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K59" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>bootloop</t>
         </is>
       </c>
       <c r="L59" s="4" t="inlineStr">
         <is>
-          <t>L5 board ID</t>
+          <t>L3</t>
         </is>
       </c>
       <c r="M59" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N59" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q59" s="4" t="inlineStr">
-        <is>
-          <t>Estante C</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q59" s="4" t="inlineStr"/>
       <c r="R59" s="4" t="inlineStr">
         <is>
-          <t>Tablet</t>
-        </is>
-      </c>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S59" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T59" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U59" s="4" t="inlineStr">
+        <is>
+          <t>Hub 2</t>
+        </is>
+      </c>
+      <c r="V59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="4" t="inlineStr">
@@ -5461,17 +6345,17 @@
       </c>
       <c r="B60" s="4" t="inlineStr">
         <is>
-          <t>Lenovo</t>
+          <t>vivo</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
         <is>
-          <t>Tab M10</t>
+          <t>Y21</t>
         </is>
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>TB-X306X / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
@@ -5481,69 +6365,81 @@
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>MT6762 Helio P22</t>
+          <t>MT6769 Helio G80</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H60" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>brom_mtk</t>
         </is>
       </c>
       <c r="I60" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J60" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K60" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L60" s="4" t="inlineStr">
         <is>
-          <t>L5 board ID</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M60" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N60" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q60" s="4" t="inlineStr">
-        <is>
-          <t>Estante C</t>
-        </is>
-      </c>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q60" s="4" t="inlineStr"/>
       <c r="R60" s="4" t="inlineStr">
         <is>
-          <t>Tablet</t>
-        </is>
-      </c>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S60" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T60" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U60" s="4" t="inlineStr">
+        <is>
+          <t>Hub 2</t>
+        </is>
+      </c>
+      <c r="V60" s="4" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="4" t="inlineStr">
@@ -5553,85 +6449,101 @@
       </c>
       <c r="B61" s="4" t="inlineStr">
         <is>
-          <t>Samsung</t>
+          <t>Honor</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
         <is>
-          <t>Galaxy A04</t>
+          <t>X7</t>
         </is>
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>SM-A045M / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>Qualcomm</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>MT6765 Helio P35</t>
+          <t>SM6225 Snapdragon 680</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H61" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>edl_qc</t>
         </is>
       </c>
       <c r="I61" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J61" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K61" s="4" t="inlineStr">
         <is>
-          <t>Bootloop</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L61" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M61" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N61" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q61" s="4" t="inlineStr">
-        <is>
-          <t>Estante A</t>
-        </is>
-      </c>
-      <c r="R61" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q61" s="4" t="inlineStr"/>
+      <c r="R61" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S61" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T61" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U61" s="4" t="inlineStr">
+        <is>
+          <t>Estante C</t>
+        </is>
+      </c>
+      <c r="V61" s="4" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="4" t="inlineStr">
@@ -5641,87 +6553,103 @@
       </c>
       <c r="B62" s="4" t="inlineStr">
         <is>
-          <t>Xiaomi</t>
+          <t>Huawei</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
         <is>
-          <t>Redmi A2</t>
+          <t>Y6p</t>
         </is>
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>23026RN54G / Global</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>MediaTek</t>
+          <t>HiSilicon</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>MT6761 Helio A22</t>
+          <t>Kirin 710A</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H62" s="4" t="inlineStr">
         <is>
-          <t>BROM / Preloader (MTK)</t>
+          <t>adb_only</t>
         </is>
       </c>
       <c r="I62" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J62" s="4" t="inlineStr">
         <is>
-          <t>Bloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K62" s="4" t="inlineStr">
         <is>
-          <t>No enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L62" s="4" t="inlineStr">
         <is>
-          <t>L3 GPT</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M62" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N62" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>no</t>
         </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="Q62" s="4" t="inlineStr">
-        <is>
-          <t>Caja pendientes</t>
-        </is>
-      </c>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q62" s="4" t="inlineStr"/>
       <c r="R62" s="4" t="inlineStr">
         <is>
-          <t>Gama de entrada</t>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S62" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T62" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U62" s="4" t="inlineStr">
+        <is>
+          <t>Estante C</t>
+        </is>
+      </c>
+      <c r="V62" s="4" t="inlineStr">
+        <is>
+          <t>Bootloader cerrado: sin ruta de escritura</t>
         </is>
       </c>
     </row>
@@ -5733,17 +6661,17 @@
       </c>
       <c r="B63" s="4" t="inlineStr">
         <is>
-          <t>Motorola</t>
+          <t>Nokia</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
         <is>
-          <t>Moto E13</t>
+          <t>G21</t>
         </is>
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>XT2345-1 / LATAM</t>
+          <t>MX</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
@@ -5758,60 +6686,76 @@
       </c>
       <c r="G63" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H63" s="4" t="inlineStr">
         <is>
-          <t>FDL (Unisoc)</t>
+          <t>fdl_unisoc</t>
         </is>
       </c>
       <c r="I63" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>none</t>
         </is>
       </c>
       <c r="J63" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>unlocked</t>
         </is>
       </c>
       <c r="K63" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L63" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L4</t>
         </is>
       </c>
       <c r="M63" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N63" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q63" s="4" t="inlineStr">
-        <is>
-          <t>Estante A</t>
-        </is>
-      </c>
-      <c r="R63" s="4" t="inlineStr"/>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q63" s="4" t="inlineStr"/>
+      <c r="R63" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S63" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T63" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U63" s="4" t="inlineStr">
+        <is>
+          <t>Estante C</t>
+        </is>
+      </c>
+      <c r="V63" s="4" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="4" t="inlineStr">
@@ -5821,85 +6765,109 @@
       </c>
       <c r="B64" s="4" t="inlineStr">
         <is>
-          <t>Tecno</t>
+          <t>Google</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
         <is>
-          <t>Spark 10</t>
+          <t>Pixel 6</t>
         </is>
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>KI5 / LATAM</t>
+          <t>US-UNLOCK</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Unisoc</t>
+          <t>Google Tensor</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>T606</t>
+          <t>Tensor G1</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
         <is>
-          <t>Android</t>
+          <t>android</t>
         </is>
       </c>
       <c r="H64" s="4" t="inlineStr">
         <is>
-          <t>FDL (Unisoc)</t>
+          <t>fastboot</t>
         </is>
       </c>
       <c r="I64" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>third_party</t>
         </is>
       </c>
       <c r="J64" s="4" t="inlineStr">
         <is>
-          <t>Desbloqueado</t>
+          <t>locked</t>
         </is>
       </c>
       <c r="K64" s="4" t="inlineStr">
         <is>
-          <t>Funciona / enciende</t>
+          <t>boots</t>
         </is>
       </c>
       <c r="L64" s="4" t="inlineStr">
         <is>
-          <t>L4 build.prop</t>
+          <t>L6</t>
         </is>
       </c>
       <c r="M64" s="4" t="inlineStr">
         <is>
-          <t>Si</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="N64" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>no</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>partial</t>
         </is>
       </c>
       <c r="Q64" s="4" t="inlineStr">
         <is>
-          <t>Caja pendientes</t>
-        </is>
-      </c>
-      <c r="R64" s="4" t="inlineStr"/>
+          <t>google</t>
+        </is>
+      </c>
+      <c r="R64" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S64" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T64" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U64" s="4" t="inlineStr">
+        <is>
+          <t>Rack de caos</t>
+        </is>
+      </c>
+      <c r="V64" s="4" t="inlineStr">
+        <is>
+          <t>EDL restringido, solo fastboot firmado</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="4" t="inlineStr">
@@ -5909,300 +6877,1420 @@
       </c>
       <c r="B65" s="4" t="inlineStr">
         <is>
+          <t>Google</t>
+        </is>
+      </c>
+      <c r="C65" s="4" t="inlineStr">
+        <is>
+          <t>Pixel 7</t>
+        </is>
+      </c>
+      <c r="D65" s="4" t="inlineStr">
+        <is>
+          <t>US-VERIZON</t>
+        </is>
+      </c>
+      <c r="E65" s="4" t="inlineStr">
+        <is>
+          <t>Google Tensor</t>
+        </is>
+      </c>
+      <c r="F65" s="4" t="inlineStr">
+        <is>
+          <t>Tensor G2</t>
+        </is>
+      </c>
+      <c r="G65" s="4" t="inlineStr">
+        <is>
+          <t>android</t>
+        </is>
+      </c>
+      <c r="H65" s="4" t="inlineStr">
+        <is>
+          <t>fastboot</t>
+        </is>
+      </c>
+      <c r="I65" s="4" t="inlineStr">
+        <is>
+          <t>third_party</t>
+        </is>
+      </c>
+      <c r="J65" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="K65" s="4" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="L65" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="M65" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="O65" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P65" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q65" s="4" t="inlineStr">
+        <is>
+          <t>verizon</t>
+        </is>
+      </c>
+      <c r="R65" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S65" s="4" t="inlineStr">
+        <is>
+          <t>carrier_automatic</t>
+        </is>
+      </c>
+      <c r="T65" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U65" s="4" t="inlineStr">
+        <is>
+          <t>Rack de caos</t>
+        </is>
+      </c>
+      <c r="V65" s="4" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" s="4" t="inlineStr">
+        <is>
+          <t>BF-061</t>
+        </is>
+      </c>
+      <c r="B66" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C66" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 8 US</t>
+        </is>
+      </c>
+      <c r="D66" s="4" t="inlineStr">
+        <is>
+          <t>US-ATT</t>
+        </is>
+      </c>
+      <c r="E66" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F66" s="4" t="inlineStr">
+        <is>
+          <t>A11 Bionic</t>
+        </is>
+      </c>
+      <c r="G66" s="4" t="inlineStr">
+        <is>
+          <t>ios</t>
+        </is>
+      </c>
+      <c r="H66" s="4" t="inlineStr">
+        <is>
+          <t>dfu_apple</t>
+        </is>
+      </c>
+      <c r="I66" s="4" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="J66" s="4" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="K66" s="4" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="L66" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="M66" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O66" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P66" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q66" s="4" t="inlineStr">
+        <is>
+          <t>att</t>
+        </is>
+      </c>
+      <c r="R66" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S66" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T66" s="4" t="inlineStr">
+        <is>
+          <t>physical_single</t>
+        </is>
+      </c>
+      <c r="U66" s="4" t="inlineStr">
+        <is>
+          <t>Estante C</t>
+        </is>
+      </c>
+      <c r="V66" s="4" t="inlineStr">
+        <is>
+          <t>Restore solo a version firmada</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="4" t="inlineStr">
+        <is>
+          <t>BF-062</t>
+        </is>
+      </c>
+      <c r="B67" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C67" s="4" t="inlineStr">
+        <is>
+          <t>iPhone XR US</t>
+        </is>
+      </c>
+      <c r="D67" s="4" t="inlineStr">
+        <is>
+          <t>US-TMOBILE</t>
+        </is>
+      </c>
+      <c r="E67" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F67" s="4" t="inlineStr">
+        <is>
+          <t>A12 Bionic</t>
+        </is>
+      </c>
+      <c r="G67" s="4" t="inlineStr">
+        <is>
+          <t>ios</t>
+        </is>
+      </c>
+      <c r="H67" s="4" t="inlineStr">
+        <is>
+          <t>dfu_apple</t>
+        </is>
+      </c>
+      <c r="I67" s="4" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="J67" s="4" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="K67" s="4" t="inlineStr">
+        <is>
+          <t>bootloop</t>
+        </is>
+      </c>
+      <c r="L67" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="M67" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O67" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P67" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q67" s="4" t="inlineStr">
+        <is>
+          <t>tmobile</t>
+        </is>
+      </c>
+      <c r="R67" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S67" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T67" s="4" t="inlineStr">
+        <is>
+          <t>physical_single</t>
+        </is>
+      </c>
+      <c r="U67" s="4" t="inlineStr">
+        <is>
+          <t>Estante C</t>
+        </is>
+      </c>
+      <c r="V67" s="4" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="4" t="inlineStr">
+        <is>
+          <t>BF-063</t>
+        </is>
+      </c>
+      <c r="B68" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C68" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 11 US</t>
+        </is>
+      </c>
+      <c r="D68" s="4" t="inlineStr">
+        <is>
+          <t>US-ATT</t>
+        </is>
+      </c>
+      <c r="E68" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F68" s="4" t="inlineStr">
+        <is>
+          <t>A13 Bionic</t>
+        </is>
+      </c>
+      <c r="G68" s="4" t="inlineStr">
+        <is>
+          <t>ios</t>
+        </is>
+      </c>
+      <c r="H68" s="4" t="inlineStr">
+        <is>
+          <t>dfu_apple</t>
+        </is>
+      </c>
+      <c r="I68" s="4" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="J68" s="4" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="K68" s="4" t="inlineStr">
+        <is>
+          <t>recovery_only</t>
+        </is>
+      </c>
+      <c r="L68" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="M68" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O68" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P68" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q68" s="4" t="inlineStr">
+        <is>
+          <t>att</t>
+        </is>
+      </c>
+      <c r="R68" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S68" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T68" s="4" t="inlineStr">
+        <is>
+          <t>physical_single</t>
+        </is>
+      </c>
+      <c r="U68" s="4" t="inlineStr">
+        <is>
+          <t>Estante C</t>
+        </is>
+      </c>
+      <c r="V68" s="4" t="inlineStr">
+        <is>
+          <t>Salida de recovery y restore firmado</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="4" t="inlineStr">
+        <is>
+          <t>BF-064</t>
+        </is>
+      </c>
+      <c r="B69" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 12</t>
+        </is>
+      </c>
+      <c r="D69" s="4" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="E69" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F69" s="4" t="inlineStr">
+        <is>
+          <t>A14 Bionic</t>
+        </is>
+      </c>
+      <c r="G69" s="4" t="inlineStr">
+        <is>
+          <t>ios</t>
+        </is>
+      </c>
+      <c r="H69" s="4" t="inlineStr">
+        <is>
+          <t>dfu_apple</t>
+        </is>
+      </c>
+      <c r="I69" s="4" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="J69" s="4" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="K69" s="4" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="L69" s="4" t="inlineStr">
+        <is>
+          <t>L6</t>
+        </is>
+      </c>
+      <c r="M69" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O69" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P69" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="Q69" s="4" t="inlineStr"/>
+      <c r="R69" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S69" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T69" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U69" s="4" t="inlineStr">
+        <is>
+          <t>Estante C</t>
+        </is>
+      </c>
+      <c r="V69" s="4" t="inlineStr">
+        <is>
+          <t>Backup completo con credenciales del dueño</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="4" t="inlineStr">
+        <is>
+          <t>BF-065</t>
+        </is>
+      </c>
+      <c r="B70" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>iPhone 14 US</t>
+        </is>
+      </c>
+      <c r="D70" s="4" t="inlineStr">
+        <is>
+          <t>US-METRO</t>
+        </is>
+      </c>
+      <c r="E70" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F70" s="4" t="inlineStr">
+        <is>
+          <t>A15 Bionic</t>
+        </is>
+      </c>
+      <c r="G70" s="4" t="inlineStr">
+        <is>
+          <t>ios</t>
+        </is>
+      </c>
+      <c r="H70" s="4" t="inlineStr">
+        <is>
+          <t>dfu_apple</t>
+        </is>
+      </c>
+      <c r="I70" s="4" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="J70" s="4" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="K70" s="4" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="L70" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="M70" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O70" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P70" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q70" s="4" t="inlineStr">
+        <is>
+          <t>metro</t>
+        </is>
+      </c>
+      <c r="R70" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S70" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T70" s="4" t="inlineStr">
+        <is>
+          <t>esim_only</t>
+        </is>
+      </c>
+      <c r="U70" s="4" t="inlineStr">
+        <is>
+          <t>Estante C</t>
+        </is>
+      </c>
+      <c r="V70" s="4" t="inlineStr">
+        <is>
+          <t>eSIM unicamente: no acepta SIM fisica mexicana</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>BF-066</t>
+        </is>
+      </c>
+      <c r="B71" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>iPhone SE 2020 US</t>
+        </is>
+      </c>
+      <c r="D71" s="4" t="inlineStr">
+        <is>
+          <t>US-VERIZON</t>
+        </is>
+      </c>
+      <c r="E71" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F71" s="4" t="inlineStr">
+        <is>
+          <t>A13 Bionic</t>
+        </is>
+      </c>
+      <c r="G71" s="4" t="inlineStr">
+        <is>
+          <t>ios</t>
+        </is>
+      </c>
+      <c r="H71" s="4" t="inlineStr">
+        <is>
+          <t>dfu_apple</t>
+        </is>
+      </c>
+      <c r="I71" s="4" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="J71" s="4" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="K71" s="4" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="L71" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="M71" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O71" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P71" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q71" s="4" t="inlineStr">
+        <is>
+          <t>verizon</t>
+        </is>
+      </c>
+      <c r="R71" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S71" s="4" t="inlineStr">
+        <is>
+          <t>carrier_automatic</t>
+        </is>
+      </c>
+      <c r="T71" s="4" t="inlineStr">
+        <is>
+          <t>physical_single</t>
+        </is>
+      </c>
+      <c r="U71" s="4" t="inlineStr">
+        <is>
+          <t>Estante C</t>
+        </is>
+      </c>
+      <c r="V71" s="4" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" s="4" t="inlineStr">
+        <is>
+          <t>BF-067</t>
+        </is>
+      </c>
+      <c r="B72" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="C72" s="4" t="inlineStr">
+        <is>
+          <t>iPad 9</t>
+        </is>
+      </c>
+      <c r="D72" s="4" t="inlineStr">
+        <is>
+          <t>MX</t>
+        </is>
+      </c>
+      <c r="E72" s="4" t="inlineStr">
+        <is>
+          <t>Apple</t>
+        </is>
+      </c>
+      <c r="F72" s="4" t="inlineStr">
+        <is>
+          <t>A13 Bionic</t>
+        </is>
+      </c>
+      <c r="G72" s="4" t="inlineStr">
+        <is>
+          <t>ios</t>
+        </is>
+      </c>
+      <c r="H72" s="4" t="inlineStr">
+        <is>
+          <t>dfu_apple</t>
+        </is>
+      </c>
+      <c r="I72" s="4" t="inlineStr">
+        <is>
+          <t>own</t>
+        </is>
+      </c>
+      <c r="J72" s="4" t="inlineStr">
+        <is>
+          <t>na</t>
+        </is>
+      </c>
+      <c r="K72" s="4" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="L72" s="4" t="inlineStr">
+        <is>
+          <t>L5</t>
+        </is>
+      </c>
+      <c r="M72" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O72" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P72" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q72" s="4" t="inlineStr"/>
+      <c r="R72" s="4" t="inlineStr">
+        <is>
+          <t>unlocked</t>
+        </is>
+      </c>
+      <c r="S72" s="4" t="inlineStr">
+        <is>
+          <t>not_needed</t>
+        </is>
+      </c>
+      <c r="T72" s="4" t="inlineStr">
+        <is>
+          <t>physical_single</t>
+        </is>
+      </c>
+      <c r="U72" s="4" t="inlineStr">
+        <is>
+          <t>Estante C</t>
+        </is>
+      </c>
+      <c r="V72" s="4" t="inlineStr">
+        <is>
+          <t>Tablet</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="4" t="inlineStr">
+        <is>
+          <t>BF-068</t>
+        </is>
+      </c>
+      <c r="B73" s="4" t="inlineStr">
+        <is>
           <t>Samsung</t>
         </is>
       </c>
-      <c r="C65" s="4" t="inlineStr">
-        <is>
-          <t>Galaxy A54 5G</t>
-        </is>
-      </c>
-      <c r="D65" s="4" t="inlineStr">
-        <is>
-          <t>SM-A546E / LATAM</t>
-        </is>
-      </c>
-      <c r="E65" s="4" t="inlineStr">
-        <is>
-          <t>Exynos</t>
-        </is>
-      </c>
-      <c r="F65" s="4" t="inlineStr">
-        <is>
-          <t>Exynos 1380</t>
-        </is>
-      </c>
-      <c r="G65" s="4" t="inlineStr">
-        <is>
-          <t>Android</t>
-        </is>
-      </c>
-      <c r="H65" s="4" t="inlineStr">
-        <is>
-          <t>EUB (Exynos)</t>
-        </is>
-      </c>
-      <c r="I65" s="4" t="inlineStr">
-        <is>
-          <t>Desconocido</t>
-        </is>
-      </c>
-      <c r="J65" s="4" t="inlineStr">
-        <is>
-          <t>Bloqueado</t>
-        </is>
-      </c>
-      <c r="K65" s="4" t="inlineStr">
-        <is>
-          <t>Funciona / enciende</t>
-        </is>
-      </c>
-      <c r="L65" s="4" t="inlineStr">
-        <is>
-          <t>L4 build.prop</t>
-        </is>
-      </c>
-      <c r="M65" s="4" t="inlineStr">
-        <is>
-          <t>Si</t>
-        </is>
-      </c>
-      <c r="N65" s="4" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="O65" s="4" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="P65" s="4" t="inlineStr">
-        <is>
-          <t>Parcial</t>
-        </is>
-      </c>
-      <c r="Q65" s="4" t="inlineStr">
-        <is>
-          <t>Estante B</t>
-        </is>
-      </c>
-      <c r="R65" s="4" t="inlineStr">
-        <is>
-          <t>Modelo reciente: token de fabricante para escritura</t>
-        </is>
-      </c>
+      <c r="C73" s="4" t="inlineStr">
+        <is>
+          <t>Galaxy A03s</t>
+        </is>
+      </c>
+      <c r="D73" s="4" t="inlineStr">
+        <is>
+          <t>US-METRO</t>
+        </is>
+      </c>
+      <c r="E73" s="4" t="inlineStr">
+        <is>
+          <t>MediaTek</t>
+        </is>
+      </c>
+      <c r="F73" s="4" t="inlineStr">
+        <is>
+          <t>MT6765 Helio P35</t>
+        </is>
+      </c>
+      <c r="G73" s="4" t="inlineStr">
+        <is>
+          <t>android</t>
+        </is>
+      </c>
+      <c r="H73" s="4" t="inlineStr">
+        <is>
+          <t>brom_mtk</t>
+        </is>
+      </c>
+      <c r="I73" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J73" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="K73" s="4" t="inlineStr">
+        <is>
+          <t>bootloop</t>
+        </is>
+      </c>
+      <c r="L73" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="M73" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="O73" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P73" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q73" s="4" t="inlineStr">
+        <is>
+          <t>metro</t>
+        </is>
+      </c>
+      <c r="R73" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S73" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T73" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U73" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V73" s="4" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="A74" s="4" t="inlineStr">
+        <is>
+          <t>BF-069</t>
+        </is>
+      </c>
+      <c r="B74" s="4" t="inlineStr">
+        <is>
+          <t>Motorola</t>
+        </is>
+      </c>
+      <c r="C74" s="4" t="inlineStr">
+        <is>
+          <t>Moto G Play 2023</t>
+        </is>
+      </c>
+      <c r="D74" s="4" t="inlineStr">
+        <is>
+          <t>US-ATT</t>
+        </is>
+      </c>
+      <c r="E74" s="4" t="inlineStr">
+        <is>
+          <t>MediaTek</t>
+        </is>
+      </c>
+      <c r="F74" s="4" t="inlineStr">
+        <is>
+          <t>MT6765H Helio G37</t>
+        </is>
+      </c>
+      <c r="G74" s="4" t="inlineStr">
+        <is>
+          <t>android</t>
+        </is>
+      </c>
+      <c r="H74" s="4" t="inlineStr">
+        <is>
+          <t>brom_mtk</t>
+        </is>
+      </c>
+      <c r="I74" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J74" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="K74" s="4" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="L74" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="M74" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="O74" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P74" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q74" s="4" t="inlineStr">
+        <is>
+          <t>att</t>
+        </is>
+      </c>
+      <c r="R74" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S74" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T74" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U74" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V74" s="4" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" s="4" t="inlineStr">
+        <is>
+          <t>BF-070</t>
+        </is>
+      </c>
+      <c r="B75" s="4" t="inlineStr">
+        <is>
+          <t>TCL</t>
+        </is>
+      </c>
+      <c r="C75" s="4" t="inlineStr">
+        <is>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="D75" s="4" t="inlineStr">
+        <is>
+          <t>US-BOOST</t>
+        </is>
+      </c>
+      <c r="E75" s="4" t="inlineStr">
+        <is>
+          <t>MediaTek</t>
+        </is>
+      </c>
+      <c r="F75" s="4" t="inlineStr">
+        <is>
+          <t>MT6761 Helio A22</t>
+        </is>
+      </c>
+      <c r="G75" s="4" t="inlineStr">
+        <is>
+          <t>android</t>
+        </is>
+      </c>
+      <c r="H75" s="4" t="inlineStr">
+        <is>
+          <t>brom_mtk</t>
+        </is>
+      </c>
+      <c r="I75" s="4" t="inlineStr">
+        <is>
+          <t>none</t>
+        </is>
+      </c>
+      <c r="J75" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="K75" s="4" t="inlineStr">
+        <is>
+          <t>noboot</t>
+        </is>
+      </c>
+      <c r="L75" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="M75" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="O75" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P75" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q75" s="4" t="inlineStr">
+        <is>
+          <t>boost</t>
+        </is>
+      </c>
+      <c r="R75" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S75" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T75" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U75" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V75" s="4" t="inlineStr">
+        <is>
+          <t>Prepago bloqueado</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="4" t="inlineStr">
+        <is>
+          <t>BF-071</t>
+        </is>
+      </c>
+      <c r="B76" s="4" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="C76" s="4" t="inlineStr">
+        <is>
+          <t>Galaxy A13 5G</t>
+        </is>
+      </c>
+      <c r="D76" s="4" t="inlineStr">
+        <is>
+          <t>US-CRICKET</t>
+        </is>
+      </c>
+      <c r="E76" s="4" t="inlineStr">
+        <is>
+          <t>MediaTek</t>
+        </is>
+      </c>
+      <c r="F76" s="4" t="inlineStr">
+        <is>
+          <t>MT6833 Dimensity 700</t>
+        </is>
+      </c>
+      <c r="G76" s="4" t="inlineStr">
+        <is>
+          <t>android</t>
+        </is>
+      </c>
+      <c r="H76" s="4" t="inlineStr">
+        <is>
+          <t>brom_mtk</t>
+        </is>
+      </c>
+      <c r="I76" s="4" t="inlineStr">
+        <is>
+          <t>third_party</t>
+        </is>
+      </c>
+      <c r="J76" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="K76" s="4" t="inlineStr">
+        <is>
+          <t>bootloop</t>
+        </is>
+      </c>
+      <c r="L76" s="4" t="inlineStr">
+        <is>
+          <t>L3</t>
+        </is>
+      </c>
+      <c r="M76" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="O76" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P76" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="Q76" s="4" t="inlineStr">
+        <is>
+          <t>cricket</t>
+        </is>
+      </c>
+      <c r="R76" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S76" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T76" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U76" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V76" s="4" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" s="4" t="inlineStr">
+        <is>
+          <t>BF-072</t>
+        </is>
+      </c>
+      <c r="B77" s="4" t="inlineStr">
+        <is>
+          <t>Samsung</t>
+        </is>
+      </c>
+      <c r="C77" s="4" t="inlineStr">
+        <is>
+          <t>Galaxy S24 Ultra</t>
+        </is>
+      </c>
+      <c r="D77" s="4" t="inlineStr">
+        <is>
+          <t>US-TMOBILE</t>
+        </is>
+      </c>
+      <c r="E77" s="4" t="inlineStr">
+        <is>
+          <t>Qualcomm</t>
+        </is>
+      </c>
+      <c r="F77" s="4" t="inlineStr">
+        <is>
+          <t>SM8650 Snapdragon 8 Gen 3</t>
+        </is>
+      </c>
+      <c r="G77" s="4" t="inlineStr">
+        <is>
+          <t>android</t>
+        </is>
+      </c>
+      <c r="H77" s="4" t="inlineStr">
+        <is>
+          <t>edl_qc</t>
+        </is>
+      </c>
+      <c r="I77" s="4" t="inlineStr">
+        <is>
+          <t>third_party</t>
+        </is>
+      </c>
+      <c r="J77" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="K77" s="4" t="inlineStr">
+        <is>
+          <t>boots</t>
+        </is>
+      </c>
+      <c r="L77" s="4" t="inlineStr">
+        <is>
+          <t>L4</t>
+        </is>
+      </c>
+      <c r="M77" s="4" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="O77" s="4" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="P77" s="4" t="inlineStr">
+        <is>
+          <t>partial</t>
+        </is>
+      </c>
+      <c r="Q77" s="4" t="inlineStr">
+        <is>
+          <t>tmobile</t>
+        </is>
+      </c>
+      <c r="R77" s="4" t="inlineStr">
+        <is>
+          <t>locked</t>
+        </is>
+      </c>
+      <c r="S77" s="4" t="inlineStr">
+        <is>
+          <t>carrier_portal</t>
+        </is>
+      </c>
+      <c r="T77" s="4" t="inlineStr">
+        <is>
+          <t>physical_dual</t>
+        </is>
+      </c>
+      <c r="U77" s="4" t="inlineStr">
+        <is>
+          <t>Estante D</t>
+        </is>
+      </c>
+      <c r="V77" s="4" t="inlineStr"/>
     </row>
   </sheetData>
-  <autoFilter ref="A5:R65"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C21"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="26" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="5" t="inlineStr">
-        <is>
-          <t>RESUMEN PROVISIONAL — calculado desde datos de ejemplo</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>No usar para decidir alcance. La matriz válida se calcula desde el inventario real del banco.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Equipos por mecanismo</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>BROM / Preloader (MTK)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>20</v>
-      </c>
-      <c r="C5" s="8" t="n">
-        <v>0.3333333333333333</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
-        <is>
-          <t>FDL (Unisoc)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>13</v>
-      </c>
-      <c r="C6" s="8" t="n">
-        <v>0.2166666666666667</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>EDL 9008 + Sahara (QC)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>12</v>
-      </c>
-      <c r="C7" s="8" t="n">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="7" t="inlineStr">
-        <is>
-          <t>DFU (Apple)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>6</v>
-      </c>
-      <c r="C8" s="8" t="n">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="7" t="inlineStr">
-        <is>
-          <t>EUB (Exynos)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>4</v>
-      </c>
-      <c r="C9" s="8" t="n">
-        <v>0.06666666666666667</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="7" t="inlineStr">
-        <is>
-          <t>Fastboot</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>3</v>
-      </c>
-      <c r="C10" s="8" t="n">
-        <v>0.05</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="7" t="inlineStr">
-        <is>
-          <t>Solo ADB</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C11" s="8" t="n">
-        <v>0.03333333333333333</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
-        <is>
-          <t>Equipos por fabricante de SoC</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="7" t="inlineStr">
-        <is>
-          <t>MediaTek</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr">
-        <is>
-          <t>Qualcomm</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="7" t="inlineStr">
-        <is>
-          <t>Unisoc</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="7" t="inlineStr">
-        <is>
-          <t>Apple</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="7" t="inlineStr">
-        <is>
-          <t>Exynos</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="7" t="inlineStr">
-        <is>
-          <t>HiSilicon</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="7" t="inlineStr">
-        <is>
-          <t>Google Tensor</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
+  <autoFilter ref="A5:V77"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>